--- a/artfynd/A 21691-2024 artfynd.xlsx
+++ b/artfynd/A 21691-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121551767</v>
+        <v>121551766</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>94516</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543758</v>
+        <v>543681</v>
       </c>
       <c r="R2" t="n">
-        <v>6287985</v>
+        <v>6288006</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121551766</v>
+        <v>121551767</v>
       </c>
       <c r="B3" t="n">
-        <v>94516</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543681</v>
+        <v>543758</v>
       </c>
       <c r="R3" t="n">
-        <v>6288006</v>
+        <v>6287985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 21691-2024 artfynd.xlsx
+++ b/artfynd/A 21691-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121551766</v>
+        <v>121551769</v>
       </c>
       <c r="B2" t="n">
-        <v>94516</v>
+        <v>5192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543681</v>
+        <v>543744</v>
       </c>
       <c r="R2" t="n">
-        <v>6288006</v>
+        <v>6287959</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121551767</v>
+        <v>121551766</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>94517</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543758</v>
+        <v>543681</v>
       </c>
       <c r="R3" t="n">
-        <v>6287985</v>
+        <v>6288006</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121551763</v>
+        <v>121551767</v>
       </c>
       <c r="B4" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543598</v>
+        <v>543758</v>
       </c>
       <c r="R4" t="n">
-        <v>6288043</v>
+        <v>6287985</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551769</v>
+        <v>121551763</v>
       </c>
       <c r="B5" t="n">
-        <v>5192</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543744</v>
+        <v>543598</v>
       </c>
       <c r="R5" t="n">
-        <v>6287959</v>
+        <v>6288043</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21691-2024 artfynd.xlsx
+++ b/artfynd/A 21691-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121551769</v>
+        <v>121551766</v>
       </c>
       <c r="B2" t="n">
-        <v>5192</v>
+        <v>94517</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543744</v>
+        <v>543681</v>
       </c>
       <c r="R2" t="n">
-        <v>6287959</v>
+        <v>6288006</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121551766</v>
+        <v>121551769</v>
       </c>
       <c r="B3" t="n">
-        <v>94517</v>
+        <v>5192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543681</v>
+        <v>543744</v>
       </c>
       <c r="R3" t="n">
-        <v>6288006</v>
+        <v>6287959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 21691-2024 artfynd.xlsx
+++ b/artfynd/A 21691-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121551766</v>
+        <v>121551767</v>
       </c>
       <c r="B2" t="n">
-        <v>94517</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543681</v>
+        <v>543758</v>
       </c>
       <c r="R2" t="n">
-        <v>6288006</v>
+        <v>6287985</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121551767</v>
+        <v>121551763</v>
       </c>
       <c r="B4" t="n">
         <v>57372</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543758</v>
+        <v>543598</v>
       </c>
       <c r="R4" t="n">
-        <v>6287985</v>
+        <v>6288043</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551763</v>
+        <v>121551766</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>94517</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543598</v>
+        <v>543681</v>
       </c>
       <c r="R5" t="n">
-        <v>6288043</v>
+        <v>6288006</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21691-2024 artfynd.xlsx
+++ b/artfynd/A 21691-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121551767</v>
+        <v>121551763</v>
       </c>
       <c r="B2" t="n">
         <v>57372</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543758</v>
+        <v>543598</v>
       </c>
       <c r="R2" t="n">
-        <v>6287985</v>
+        <v>6288043</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121551769</v>
+        <v>121551767</v>
       </c>
       <c r="B3" t="n">
-        <v>5192</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543744</v>
+        <v>543758</v>
       </c>
       <c r="R3" t="n">
-        <v>6287959</v>
+        <v>6287985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121551763</v>
+        <v>121551769</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>5192</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,20 +909,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543598</v>
+        <v>543744</v>
       </c>
       <c r="R4" t="n">
-        <v>6288043</v>
+        <v>6287959</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 21691-2024 artfynd.xlsx
+++ b/artfynd/A 21691-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121551766</v>
+        <v>121551769</v>
       </c>
       <c r="B3" t="n">
-        <v>94525</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543681</v>
+        <v>543744</v>
       </c>
       <c r="R3" t="n">
-        <v>6288006</v>
+        <v>6287959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121551769</v>
+        <v>121551763</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,20 +909,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543744</v>
+        <v>543598</v>
       </c>
       <c r="R4" t="n">
-        <v>6287959</v>
+        <v>6288043</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551763</v>
+        <v>121551766</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>94525</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543598</v>
+        <v>543681</v>
       </c>
       <c r="R5" t="n">
-        <v>6288043</v>
+        <v>6288006</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21691-2024 artfynd.xlsx
+++ b/artfynd/A 21691-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121551767</v>
+        <v>121551766</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>94525</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543758</v>
+        <v>543681</v>
       </c>
       <c r="R2" t="n">
-        <v>6287985</v>
+        <v>6288006</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121551763</v>
+        <v>121551767</v>
       </c>
       <c r="B4" t="n">
         <v>57373</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543598</v>
+        <v>543758</v>
       </c>
       <c r="R4" t="n">
-        <v>6288043</v>
+        <v>6287985</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551766</v>
+        <v>121551763</v>
       </c>
       <c r="B5" t="n">
-        <v>94525</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543681</v>
+        <v>543598</v>
       </c>
       <c r="R5" t="n">
-        <v>6288006</v>
+        <v>6288043</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
